--- a/output/2026-09-19_19_Croazia_Osjecko-baranjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-19_19_Croazia_Osjecko-baranjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore di utensileria industriale e da manutenzione (elettroutensili, utensili manuali, attrezzature per saldatura, taglio/mola); rappresentante marchi Elora, Komelon, Scala, Stabila, Picard, Kirschen, Olfa. Verificato tramite fininfo.hr, companywall.hr e sito ufficiale.</t>
+          <t>Distributore di utensileria industriale e da manutenzione (elettroutensili, utensili manuali, attrezzature per saldatura, taglio/mola); rappresentante marchi Elora, Komelon, Scala, Stabila, Picard, Kirschen, Olfa. Verificato tramite fininfo.hr, companywall.hr e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-16_18_Croazia_Osječko-baranjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -699,7 +699,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>majstoralata@gmail.com</t>
@@ -826,7 +825,6 @@
           <t>031 813 709</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Distributore di ricambi, utensili, DPI, macchinari e saldatrici per industria/artigianato/agricoltura, incl. cuscinetti/cinghie/catene. Attenzione: attivita' include anche vendita/assistenza macchine da giardino (Husqvarna, Cub Cadet) - focus misto, verificare pertinenza specifica prima del contatto commerciale. Email non reperita. Verificato via tvrtke.hr e djakovo.biz.</t>

--- a/output/2026-09-19_19_Croazia_Osjecko-baranjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-19_19_Croazia_Osjecko-baranjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
